--- a/import_funct_lit.xlsx
+++ b/import_funct_lit.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxsc\Nextcloud\Programs\SII\Mandarin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\max\Desktop\mandarinBandimportance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA82CA1-4CA9-47CF-A729-C990BDF25C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D29455-8794-47A1-BAE7-51AD6B621B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>cent freq</t>
   </si>
@@ -170,6 +170,15 @@
   </si>
   <si>
     <t>bad_refcond</t>
+  </si>
+  <si>
+    <t>du_2019_nonsense_sentence_interpolated</t>
+  </si>
+  <si>
+    <t>du_2019_meaningful_sentence_interpolated</t>
+  </si>
+  <si>
+    <t>du_2019_disyllabic_words_interp</t>
   </si>
 </sst>
 </file>
@@ -214,11 +223,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,7 +971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="3" width="8.44140625" customWidth="1"/>
@@ -979,10 +987,13 @@
     <col min="16" max="16" width="10.88671875" customWidth="1"/>
     <col min="17" max="18" width="8.44140625" customWidth="1"/>
     <col min="19" max="19" width="9.77734375" customWidth="1"/>
-    <col min="20" max="62" width="8.44140625" customWidth="1"/>
+    <col min="20" max="20" width="15" customWidth="1"/>
+    <col min="21" max="21" width="14.21875" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" customWidth="1"/>
+    <col min="23" max="62" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1037,11 +1048,20 @@
       <c r="R1" t="s">
         <v>42</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>143</v>
       </c>
@@ -1097,11 +1117,20 @@
       <c r="R2">
         <v>0</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2">
         <v>1.4777531610677099E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>179</v>
       </c>
@@ -1157,11 +1186,20 @@
       <c r="R3">
         <v>0</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3">
         <v>6.3570145235786704E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>224</v>
       </c>
@@ -1217,11 +1255,20 @@
       <c r="R4">
         <v>0</v>
       </c>
-      <c r="S4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>3.6316733092518802E-2</v>
+      </c>
+      <c r="U4">
+        <v>3.9370266241425499E-2</v>
+      </c>
+      <c r="V4">
+        <v>3.9370266241425499E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>281</v>
       </c>
@@ -1277,11 +1324,20 @@
       <c r="R5">
         <v>0</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5">
         <v>2.2717020817796502E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5">
+        <v>4.6943934641098001E-2</v>
+      </c>
+      <c r="U5">
+        <v>5.6421542661793403E-2</v>
+      </c>
+      <c r="V5">
+        <v>5.6421542661793403E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>355</v>
       </c>
@@ -1337,11 +1393,20 @@
       <c r="R6">
         <v>0</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6">
         <v>9.3432057756288198E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6">
+        <v>6.0841044358470701E-2</v>
+      </c>
+      <c r="U6">
+        <v>7.8719365673043704E-2</v>
+      </c>
+      <c r="V6">
+        <v>7.8719365673043704E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>447</v>
       </c>
@@ -1397,11 +1462,20 @@
       <c r="R7">
         <v>0</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7">
         <v>0.12085278024542701</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7">
+        <v>7.71905852024386E-2</v>
+      </c>
+      <c r="U7">
+        <v>0.104952098627456</v>
+      </c>
+      <c r="V7">
+        <v>0.104952098627456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>561</v>
       </c>
@@ -1457,11 +1531,20 @@
       <c r="R8">
         <v>0</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8">
         <v>8.9334724652871497E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8">
+        <v>7.7062985869951403E-2</v>
+      </c>
+      <c r="U8">
+        <v>9.8118746861359005E-2</v>
+      </c>
+      <c r="V8">
+        <v>9.8118746861359005E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9">
         <v>710</v>
       </c>
@@ -1517,11 +1600,20 @@
       <c r="R9">
         <v>0</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9">
         <v>0.14798645842643299</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9">
+        <v>7.6896125204391194E-2</v>
+      </c>
+      <c r="U9">
+        <v>8.9182825321078504E-2</v>
+      </c>
+      <c r="V9">
+        <v>8.9182825321078504E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10">
         <v>894</v>
       </c>
@@ -1577,11 +1669,20 @@
       <c r="R10">
         <v>0</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10">
         <v>6.9315248089984502E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10">
+        <v>7.6699818539026202E-2</v>
+      </c>
+      <c r="U10">
+        <v>7.8669976450160203E-2</v>
+      </c>
+      <c r="V10">
+        <v>7.8669976450160203E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11">
         <v>1118</v>
       </c>
@@ -1637,11 +1738,20 @@
       <c r="R11">
         <v>0</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11">
         <v>7.0885609783851E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11">
+        <v>8.05295512517267E-2</v>
+      </c>
+      <c r="U11">
+        <v>7.6994270673755402E-2</v>
+      </c>
+      <c r="V11">
+        <v>7.6994270673755402E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12">
         <v>1414</v>
       </c>
@@ -1697,11 +1807,20 @@
       <c r="R12">
         <v>0</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12">
         <v>1.6045340835904899E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12">
+        <v>8.58911770495073E-2</v>
+      </c>
+      <c r="U12">
+        <v>7.4648282586788794E-2</v>
+      </c>
+      <c r="V12">
+        <v>7.4648282586788794E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13">
         <v>1789</v>
       </c>
@@ -1757,11 +1876,20 @@
       <c r="R13">
         <v>0</v>
       </c>
-      <c r="S13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>9.2018749389828097E-2</v>
+      </c>
+      <c r="U13">
+        <v>7.1967153344541193E-2</v>
+      </c>
+      <c r="V13">
+        <v>7.1967153344541193E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14">
         <v>2236</v>
       </c>
@@ -1817,11 +1945,20 @@
       <c r="R14">
         <v>0</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14">
         <v>2.40917208075839E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="T14">
+        <v>8.1099191128901807E-2</v>
+      </c>
+      <c r="U14">
+        <v>6.2671396037537894E-2</v>
+      </c>
+      <c r="V14">
+        <v>6.2671396037537894E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15">
         <v>2806</v>
       </c>
@@ -1877,11 +2014,20 @@
       <c r="R15">
         <v>0</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15">
         <v>1.01306350560283E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="T15">
+        <v>6.6903765389697598E-2</v>
+      </c>
+      <c r="U15">
+        <v>5.0586911538433699E-2</v>
+      </c>
+      <c r="V15">
+        <v>5.0586911538433699E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16">
         <v>3550</v>
       </c>
@@ -1937,11 +2083,20 @@
       <c r="R16">
         <v>0</v>
       </c>
-      <c r="S16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19">
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>4.8340516346122998E-2</v>
+      </c>
+      <c r="U16">
+        <v>3.4784124116528203E-2</v>
+      </c>
+      <c r="V16">
+        <v>3.4784124116528203E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17">
         <v>4472</v>
       </c>
@@ -1997,11 +2152,20 @@
       <c r="R17">
         <v>0</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17">
         <v>1.8816737041417501E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="T17">
+        <v>4.1250690797897199E-2</v>
+      </c>
+      <c r="U17">
+        <v>3.1847229255776703E-2</v>
+      </c>
+      <c r="V17">
+        <v>3.1847229255776703E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18">
         <v>5612</v>
       </c>
@@ -2057,11 +2221,20 @@
       <c r="R18">
         <v>0</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18">
         <v>0.11276409798206</v>
       </c>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="T18">
+        <v>3.20339175852037E-2</v>
+      </c>
+      <c r="U18">
+        <v>2.8029265936799799E-2</v>
+      </c>
+      <c r="V18">
+        <v>2.8029265936799799E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19">
         <v>7099</v>
       </c>
@@ -2117,29 +2290,38 @@
       <c r="R19">
         <v>1</v>
       </c>
-      <c r="S19" s="3">
+      <c r="S19">
         <v>0.207741454701694</v>
       </c>
-    </row>
-    <row r="22" spans="1:19">
+      <c r="T19">
+        <v>1.9981214153219799E-2</v>
+      </c>
+      <c r="U19">
+        <v>2.3036544673522199E-2</v>
+      </c>
+      <c r="V19">
+        <v>2.3036544673522199E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:22">
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:22">
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:22">
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:22">
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:22">
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:22">
       <c r="H28" s="1"/>
     </row>
   </sheetData>
